--- a/TestData/TMTI0055018_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForFRLOBOpportunityEngagement.xlsx
+++ b/TestData/TMTI0055018_VerifyInternalDealTeamSpecialtyRoleIncreasedLimitForFRLOBOpportunityEngagement.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27126"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\VKumar0427\source\repos\SF_Automation\TestData\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vkumar0427\source\repos\SF_Automation\TestData\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08CA69AA-AFFF-4F0D-831A-A0704AFA5201}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4500ED49-8FB7-4448-A32C-1EC4D7047C49}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="14640" firstSheet="1" activeTab="3" xr2:uid="{6B024EC1-CFC4-4478-BEDE-727CE3160023}"/>
+    <workbookView xWindow="-23148" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6B024EC1-CFC4-4478-BEDE-727CE3160023}"/>
   </bookViews>
   <sheets>
     <sheet name="AddOpportunity" sheetId="1" r:id="rId1"/>
@@ -157,9 +157,6 @@
     <t>Accountant</t>
   </si>
   <si>
-    <t>AM</t>
-  </si>
-  <si>
     <t>HL Capital, Inc.</t>
   </si>
   <si>
@@ -344,6 +341,9 @@
   </si>
   <si>
     <t>JP Hanson</t>
+  </si>
+  <si>
+    <t>LA</t>
   </si>
 </sst>
 </file>
@@ -393,7 +393,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
@@ -408,7 +408,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -856,61 +855,61 @@
         <v>36</v>
       </c>
       <c r="K2" t="s">
+        <v>100</v>
+      </c>
+      <c r="L2" t="s">
         <v>38</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" t="s">
         <v>39</v>
       </c>
-      <c r="M2" t="s">
+      <c r="N2" t="s">
         <v>40</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="P2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="Q2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="R2" t="s">
         <v>42</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="S2" t="s">
         <v>42</v>
       </c>
-      <c r="Q2" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="R2" t="s">
+      <c r="T2" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="S2" t="s">
-        <v>43</v>
-      </c>
-      <c r="T2" s="4" t="s">
+      <c r="U2" t="s">
         <v>44</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>45</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>46</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>47</v>
       </c>
-      <c r="X2" t="s">
+      <c r="Y2" t="s">
         <v>48</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>49</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" s="4" t="s">
+        <v>41</v>
+      </c>
+      <c r="AB2" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="AA2" s="4" t="s">
-        <v>42</v>
-      </c>
-      <c r="AB2" s="4" t="s">
+      <c r="AC2" t="s">
         <v>51</v>
-      </c>
-      <c r="AC2" t="s">
-        <v>52</v>
       </c>
       <c r="AD2" t="s">
         <v>36</v>
@@ -919,7 +918,7 @@
         <v>36</v>
       </c>
       <c r="AF2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -937,15 +936,15 @@
         <v>31</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
   </sheetData>
@@ -960,54 +959,54 @@
   <sheetData>
     <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>59</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>61</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>62</v>
+      </c>
+      <c r="B2" t="s">
         <v>63</v>
       </c>
-      <c r="B2" t="s">
+      <c r="C2" t="s">
         <v>64</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>65</v>
-      </c>
-      <c r="D2" t="s">
-        <v>66</v>
       </c>
       <c r="E2" t="s">
         <v>0</v>
       </c>
       <c r="F2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G2" t="s">
         <v>0</v>
       </c>
       <c r="H2" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
   </sheetData>
@@ -1025,142 +1024,142 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="s">
-        <v>99</v>
+      <c r="A21" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1176,12 +1175,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>
@@ -1200,18 +1199,18 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
+        <v>93</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>95</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="45" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="B2" s="4" t="s">
         <v>96</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>97</v>
       </c>
     </row>
   </sheetData>
